--- a/documents/数据库设计.xlsx
+++ b/documents/数据库设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\code\WeChat\order_food\order_food\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01366729-4D06-4BDD-B401-EF60CCE61988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92050A83-8B54-4477-8D36-92400A56103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6270" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,14 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>菜品配料id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菜品配料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>用量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,18 +175,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>菜品（财务）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>分类id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>菜品财务id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>订单号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -267,10 +251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*评价id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -328,6 +308,34 @@
   </si>
   <si>
     <t>role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本单价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜品配方表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库存单位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商家id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -684,20 +692,26 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
@@ -705,22 +719,22 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="E10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
@@ -733,15 +747,21 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
       </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
         <v>0</v>
@@ -749,19 +769,19 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -770,7 +790,7 @@
         <v>20</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -778,7 +798,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -795,13 +815,13 @@
         <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
@@ -817,16 +837,16 @@
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -839,19 +859,19 @@
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -861,13 +881,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
@@ -880,7 +900,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D29" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -892,21 +912,21 @@
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N29" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O29" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P29" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -915,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
@@ -923,30 +943,27 @@
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
       </c>
       <c r="I32" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="J32" t="s">
-        <v>66</v>
-      </c>
-      <c r="K32" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
         <v>0</v>
@@ -957,21 +974,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
@@ -982,21 +985,32 @@
         <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
@@ -1025,15 +1039,18 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D46" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="F46" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
         <v>0</v>
@@ -1042,5 +1059,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/documents/数据库设计.xlsx
+++ b/documents/数据库设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\code\WeChat\order_food\order_food\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92050A83-8B54-4477-8D36-92400A56103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF823BFE-8DC2-4848-8A19-E0A1A1B81A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12765" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="78">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,18 +187,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>省</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>区县</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>具体地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -336,6 +324,14 @@
   </si>
   <si>
     <t>商家id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -661,398 +657,437 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:P47"/>
+  <dimension ref="B4:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="F4" t="s">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    <row r="5" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>2</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>3</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" t="s">
+        <v>62</v>
+      </c>
+      <c r="P29" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>64</v>
+      </c>
+      <c r="R29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>77</v>
+      </c>
+      <c r="N30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="D29" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>65</v>
-      </c>
-      <c r="N29" t="s">
-        <v>66</v>
-      </c>
-      <c r="O29" t="s">
-        <v>67</v>
-      </c>
-      <c r="P29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" t="s">
-        <v>37</v>
-      </c>
-      <c r="H32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" t="s">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
         <v>76</v>
       </c>
-      <c r="D38" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E39" t="s">
+      <c r="E38" t="s">
         <v>73</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F38" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H39" t="s">
         <v>11</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="D42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="D46" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" t="s">
         <v>0</v>
       </c>
     </row>

--- a/documents/数据库设计.xlsx
+++ b/documents/数据库设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\code\WeChat\order_food\order_food\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF823BFE-8DC2-4848-8A19-E0A1A1B81A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15960C69-FF83-4E57-81F2-30C98D1B61A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12765" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5955" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>收货地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -332,6 +328,10 @@
   </si>
   <si>
     <t>wait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入时价格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -670,7 +670,7 @@
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -691,29 +691,29 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.2">
       <c r="F8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>0</v>
@@ -721,21 +721,21 @@
     </row>
     <row r="10" spans="3:14" x14ac:dyDescent="0.2">
       <c r="G10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -743,24 +743,24 @@
     </row>
     <row r="13" spans="3:14" x14ac:dyDescent="0.2">
       <c r="F13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>0</v>
@@ -768,39 +768,39 @@
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -811,27 +811,27 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -839,74 +839,74 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" t="s">
         <v>38</v>
-      </c>
-      <c r="J21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" t="s">
         <v>38</v>
       </c>
-      <c r="J23" t="s">
-        <v>39</v>
-      </c>
       <c r="K23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" t="s">
         <v>46</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>47</v>
-      </c>
-      <c r="H25" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
         <v>0</v>
@@ -914,36 +914,36 @@
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O29" t="s">
+        <v>61</v>
+      </c>
+      <c r="P29" t="s">
         <v>62</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>63</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>64</v>
-      </c>
-      <c r="R29" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -952,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.2">
@@ -963,66 +963,66 @@
         <v>10</v>
       </c>
       <c r="H32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K32" t="s">
         <v>11</v>
       </c>
       <c r="L32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="G37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" t="s">
         <v>32</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" t="s">
         <v>33</v>
-      </c>
-      <c r="J37" t="s">
-        <v>71</v>
-      </c>
-      <c r="K37" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" t="s">
         <v>0</v>
@@ -1030,40 +1030,40 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="G39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
         <v>30</v>
-      </c>
-      <c r="E40" t="s">
-        <v>0</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
         <v>0</v>
@@ -1071,21 +1071,21 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="F46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E47" t="s">
         <v>0</v>

--- a/documents/数据库设计.xlsx
+++ b/documents/数据库设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\code\WeChat\order_food\order_food\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15960C69-FF83-4E57-81F2-30C98D1B61A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015DB6E6-CB65-4FA7-85C3-794F535204EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5955" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12390" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,14 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自取</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>支付金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>创建时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -107,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结束时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>菜品分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,34 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>预计时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际完成时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际送达时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取餐凭证id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否有效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否取餐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取餐码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>*评价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,18 +191,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>取餐时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>总支付金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>客户</t>
   </si>
   <si>
@@ -332,6 +284,38 @@
   </si>
   <si>
     <t>加入时价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预约时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预约/即时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支付时单价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜品名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际支付金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配送费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +644,7 @@
   <dimension ref="B4:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.2">
       <c r="H4" t="s">
         <v>7</v>
       </c>
@@ -668,9 +652,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -691,48 +675,48 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.2">
       <c r="F8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.2">
       <c r="G10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="3:14" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -741,66 +725,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.2">
       <c r="F13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" t="s">
         <v>17</v>
       </c>
-      <c r="I13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="M16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" t="s">
+        <v>67</v>
+      </c>
+      <c r="P16" t="s">
         <v>56</v>
       </c>
-      <c r="E14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="F16" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" t="s">
-        <v>53</v>
-      </c>
-      <c r="K16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16" t="s">
-        <v>17</v>
+      <c r="Q16" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -811,139 +804,95 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
         <v>24</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>53</v>
+      </c>
+      <c r="L18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" t="s">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
         <v>37</v>
       </c>
-      <c r="J21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" t="s">
-        <v>40</v>
-      </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K23" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="F25" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F29" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I29" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="P29" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Q29" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="R29" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -952,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N30" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.2">
@@ -963,66 +912,66 @@
         <v>10</v>
       </c>
       <c r="H32" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s">
         <v>11</v>
       </c>
       <c r="L32" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="G37" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
         <v>0</v>
@@ -1030,40 +979,40 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="G39" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="F42" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>0</v>
@@ -1071,21 +1020,21 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="F46" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E47" t="s">
         <v>0</v>
